--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="260">
   <si>
     <t>C-201(40)</t>
   </si>
@@ -136,649 +136,649 @@
     <t>16:30</t>
   </si>
   <si>
-    <t>İNM 477(49:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 313(9:1)</t>
-  </si>
-  <si>
-    <t>ÇEV 213(9:1)</t>
-  </si>
-  <si>
-    <t>JEO 209(9:6)</t>
-  </si>
-  <si>
-    <t>MAK 105(121:2)</t>
-  </si>
-  <si>
-    <t>İNM 309(78:4)</t>
-  </si>
-  <si>
-    <t>GIDA 327(88:3)</t>
-  </si>
-  <si>
-    <t>MAK 101(190:2)</t>
-  </si>
-  <si>
-    <t>JEO 317(3:6)</t>
-  </si>
-  <si>
-    <t>MAK 471(20:2)</t>
-  </si>
-  <si>
-    <t>İNM 463(44:4)</t>
-  </si>
-  <si>
-    <t>JEO 407(8:6)</t>
-  </si>
-  <si>
-    <t>MAK 103(102:2)</t>
-  </si>
-  <si>
-    <t>CSE 469(11:0)</t>
-  </si>
-  <si>
-    <t>MAK 307(118:2)</t>
-  </si>
-  <si>
-    <t>İNM 303(91:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 183(19:1)</t>
-  </si>
-  <si>
-    <t>ÇEV 303(8:1)</t>
-  </si>
-  <si>
-    <t>İNM 471(10:4)</t>
-  </si>
-  <si>
-    <t>İNM 301(112:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 179(18:1)</t>
-  </si>
-  <si>
-    <t>ÇEV 315(7:1)</t>
-  </si>
-  <si>
-    <t>İNM 211(118:4)</t>
-  </si>
-  <si>
-    <t>CSE 425(28:0)</t>
-  </si>
-  <si>
-    <t>MAK 363(25:2)</t>
-  </si>
-  <si>
-    <t>GIDA 463(21:3)</t>
-  </si>
-  <si>
-    <t>İNM 101(72:4)</t>
-  </si>
-  <si>
-    <t>İNM 491(32:4)</t>
-  </si>
-  <si>
-    <t>GIDA 101(66:3)</t>
-  </si>
-  <si>
-    <t>GIDA 351(29:3)</t>
-  </si>
-  <si>
-    <t>EEM 305(188:5)</t>
-  </si>
-  <si>
-    <t>İNM 401(65:4)</t>
-  </si>
-  <si>
-    <t>MAK 361(24:2)</t>
-  </si>
-  <si>
-    <t>EEE 499(93:5)</t>
-  </si>
-  <si>
-    <t>JEO 205(7:6)</t>
-  </si>
-  <si>
-    <t>MAK 405(59:2)</t>
-  </si>
-  <si>
-    <t>MAK 205(129:2)</t>
-  </si>
-  <si>
-    <t>EEM 209(183:5)</t>
-  </si>
-  <si>
-    <t>MAK 207(109:2)</t>
-  </si>
-  <si>
-    <t>CSE 409(56:0)</t>
-  </si>
-  <si>
-    <t>EEE 441(64:5)</t>
-  </si>
-  <si>
-    <t>JEO 307(6:6)</t>
-  </si>
-  <si>
-    <t>MAK 431(19:2)</t>
-  </si>
-  <si>
-    <t>İNM 313(84:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 353(14:1)</t>
-  </si>
-  <si>
-    <t>MTH 402(31:2)</t>
-  </si>
-  <si>
-    <t>İNM 207(139:4)</t>
-  </si>
-  <si>
-    <t>5i(833:1)</t>
-  </si>
-  <si>
-    <t>MAK 309(70:2)</t>
-  </si>
-  <si>
-    <t>ÇEV 435(17:1)</t>
-  </si>
-  <si>
-    <t>JEO 405(9:6)</t>
-  </si>
-  <si>
-    <t>İNM 473(10:4)</t>
-  </si>
-  <si>
-    <t>FİZ 173(325:0)</t>
-  </si>
-  <si>
-    <t>MAK 211(99:2)</t>
-  </si>
-  <si>
-    <t>İNM 209(99:4)</t>
-  </si>
-  <si>
-    <t>CSE 435(91:0)</t>
-  </si>
-  <si>
-    <t>JEO 203(2:6)</t>
-  </si>
-  <si>
-    <t>ÇEV 307(9:1)</t>
-  </si>
-  <si>
-    <t>EEM 201(172:5)</t>
-  </si>
-  <si>
-    <t>EEM 315(59:5)</t>
-  </si>
-  <si>
-    <t>JEO 403(7:6)</t>
-  </si>
-  <si>
-    <t>GIDA 357(37:3)</t>
-  </si>
-  <si>
-    <t>CSE 381(9:0)</t>
-  </si>
-  <si>
-    <t>CSE 433(7:0)</t>
-  </si>
-  <si>
-    <t>MAK 203(123:2)</t>
-  </si>
-  <si>
-    <t>İNM 201(64:4)</t>
-  </si>
-  <si>
-    <t>MAT 163(40:1)</t>
-  </si>
-  <si>
-    <t>MAT 151(235:5)</t>
-  </si>
-  <si>
-    <t>EEE 447(69:5)</t>
-  </si>
-  <si>
-    <t>MAT 161(114:3)</t>
-  </si>
-  <si>
-    <t>GIDA 457(32:3)</t>
-  </si>
-  <si>
-    <t>MAT 161(140:2)</t>
-  </si>
-  <si>
-    <t>MAT 161(106:4)</t>
-  </si>
-  <si>
-    <t>EEM 213(182:5)</t>
-  </si>
-  <si>
-    <t>GIDA 355(37:3)</t>
-  </si>
-  <si>
-    <t>CSE 481(91:0)</t>
-  </si>
-  <si>
-    <t>EEM 215(132:5)</t>
-  </si>
-  <si>
-    <t>GIDA 217(111:3)</t>
-  </si>
-  <si>
-    <t>İNM 205(152:4)</t>
-  </si>
-  <si>
-    <t>MAK 201(118:2)</t>
-  </si>
-  <si>
-    <t>MAK 305(62:2)</t>
-  </si>
-  <si>
-    <t>MAK 401(52:2)</t>
-  </si>
-  <si>
-    <t>MAK 301(124:2)</t>
-  </si>
-  <si>
-    <t>GIDA 215(130:3)</t>
-  </si>
-  <si>
-    <t>JEO 321(4:6)</t>
-  </si>
-  <si>
-    <t>MAK 417(20:2)</t>
-  </si>
-  <si>
-    <t>ÇEV 309(14:1)</t>
-  </si>
-  <si>
-    <t>JEO 305(5:6)</t>
-  </si>
-  <si>
-    <t>GIDA 325(103:3)</t>
-  </si>
-  <si>
-    <t>GIDA 323(97:3)</t>
-  </si>
-  <si>
-    <t>JEO 303(6:6)</t>
-  </si>
-  <si>
-    <t>JEO 201(9:6)</t>
-  </si>
-  <si>
-    <t>MAK 425(24:2)</t>
-  </si>
-  <si>
-    <t>MAK 437(15:2)</t>
-  </si>
-  <si>
-    <t>İNM 311(106:4)</t>
-  </si>
-  <si>
-    <t>KPD 101(150:5)</t>
-  </si>
-  <si>
-    <t>ÇEV 153(31:1)</t>
-  </si>
-  <si>
-    <t>KPD 101(96:2)</t>
-  </si>
-  <si>
-    <t>İNM 109(65:4)</t>
-  </si>
-  <si>
-    <t>MAK 433(15:2)</t>
-  </si>
-  <si>
-    <t>JEO 409(8:6)</t>
-  </si>
-  <si>
-    <t>GIDA 233(81:3)</t>
-  </si>
-  <si>
-    <t>GIDA 245(45:3)</t>
-  </si>
-  <si>
-    <t>GIDA 213(100:3)</t>
-  </si>
-  <si>
-    <t>CSE 301(119:0)</t>
-  </si>
-  <si>
-    <t>EEE 431(10:5)</t>
-  </si>
-  <si>
-    <t>İNM 107(104:4)</t>
-  </si>
-  <si>
-    <t>MAK 451(20:2)</t>
-  </si>
-  <si>
-    <t>CSE 303(83:0)</t>
-  </si>
-  <si>
-    <t>KİM 175(198:5)</t>
-  </si>
-  <si>
-    <t>AIE 105(8:0)</t>
-  </si>
-  <si>
-    <t>MAK 111(119:2)</t>
-  </si>
-  <si>
-    <t>İNM 493(20:4)</t>
-  </si>
-  <si>
-    <t>EEM 391(121:5)</t>
-  </si>
-  <si>
-    <t>GIDA 333(90:3)</t>
-  </si>
-  <si>
-    <t>JEO 101(16:6)</t>
-  </si>
-  <si>
-    <t>EEM 313(34:5)</t>
-  </si>
-  <si>
-    <t>CSE 377(27:0)</t>
-  </si>
-  <si>
-    <t>ÇEV 173(23:1)</t>
-  </si>
-  <si>
-    <t>İNM 307(110:4)</t>
-  </si>
-  <si>
-    <t>MAK 369(24:2)</t>
-  </si>
-  <si>
-    <t>EEE 493(59:5)</t>
-  </si>
-  <si>
-    <t>İNM 105(66:4)</t>
-  </si>
-  <si>
-    <t>GIDA 431(63:3)</t>
-  </si>
-  <si>
-    <t>GIDA 435(72:3)</t>
-  </si>
-  <si>
-    <t>GIDA 329(76:3)</t>
-  </si>
-  <si>
-    <t>GIDA 113(76:3)</t>
-  </si>
-  <si>
-    <t>ÇEV 251(26:1)</t>
-  </si>
-  <si>
-    <t>GIDA 411(32:3)</t>
-  </si>
-  <si>
-    <t>GIDA 453(29:3)</t>
-  </si>
-  <si>
-    <t>GIDA 465(35:3)</t>
-  </si>
-  <si>
-    <t>EEM 307(226:5)</t>
-  </si>
-  <si>
-    <t>ÇEV 201(25:1)</t>
-  </si>
-  <si>
-    <t>KİM 171(84:3)</t>
-  </si>
-  <si>
-    <t>GIDA 209(97:3)</t>
-  </si>
-  <si>
-    <t>MAK 303(105:2)</t>
-  </si>
-  <si>
-    <t>FİZ 167(159:3)</t>
-  </si>
-  <si>
-    <t>CSE 221(132:0)</t>
-  </si>
-  <si>
-    <t>MAK 109(131:2)</t>
-  </si>
-  <si>
-    <t>GIDA 352(33:3)</t>
-  </si>
-  <si>
-    <t>ÇEV 253(9:1)</t>
-  </si>
-  <si>
-    <t>GIDA 467(16:3)</t>
-  </si>
-  <si>
-    <t>EEM 357(92:5)</t>
-  </si>
-  <si>
-    <t>EEM 341(62:5)</t>
-  </si>
-  <si>
-    <t>CSE 211(93:0)</t>
-  </si>
-  <si>
-    <t>CSE 201(99:0)</t>
-  </si>
-  <si>
-    <t>GIDA 433(78:3)</t>
-  </si>
-  <si>
-    <t>EEE 483(79:5)</t>
-  </si>
-  <si>
-    <t>EEM 107(183:5)</t>
-  </si>
-  <si>
-    <t>EEM 207(221:5)</t>
-  </si>
-  <si>
-    <t>EEM 325(139:5)</t>
-  </si>
-  <si>
-    <t>MAK 473(19:2)</t>
-  </si>
-  <si>
-    <t>İNM 203(129:4)</t>
-  </si>
-  <si>
-    <t>EEM 323(179:5)</t>
-  </si>
-  <si>
-    <t>EEM 309(45:5)</t>
-  </si>
-  <si>
-    <t>FİZ 175(252:0)</t>
-  </si>
-  <si>
-    <t>İNM 213(168:4)</t>
-  </si>
-  <si>
-    <t>GIDA 451(29:3)</t>
-  </si>
-  <si>
-    <t>EEE 477(52:5)</t>
-  </si>
-  <si>
-    <t>EEM 217(137:5)</t>
-  </si>
-  <si>
-    <t>MAT 151(167:0)</t>
-  </si>
-  <si>
-    <t>ÇEV 205(9:1)</t>
-  </si>
-  <si>
-    <t>EEE 417(64:5)</t>
-  </si>
-  <si>
-    <t>EEM 203(220:5)</t>
-  </si>
-  <si>
-    <t>ÇEV 415(1:1)</t>
-  </si>
-  <si>
-    <t>EEE 487(26:5)</t>
-  </si>
-  <si>
-    <t>MAK 461(20:2)</t>
-  </si>
-  <si>
-    <t>MAK 209(133:2)</t>
-  </si>
-  <si>
-    <t>EEE 473(45:5)</t>
-  </si>
-  <si>
-    <t>GIDA 199(73:3)</t>
-  </si>
-  <si>
-    <t>JEO 309(8:6)</t>
-  </si>
-  <si>
-    <t>ÇEV 343(6:1)</t>
-  </si>
-  <si>
-    <t>EEE 427(93:5)</t>
-  </si>
-  <si>
-    <t>İNM 433(18:4)</t>
-  </si>
-  <si>
-    <t>İNM 453(47:4)</t>
-  </si>
-  <si>
-    <t>GIDA 239(115:3)</t>
-  </si>
-  <si>
-    <t>EEM 101(214:5)</t>
-  </si>
-  <si>
-    <t>İNM 305(129:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 409(11:1)</t>
-  </si>
-  <si>
-    <t>İNM 431(49:4)</t>
-  </si>
-  <si>
-    <t>ÇEV 417(8:1)</t>
-  </si>
-  <si>
-    <t>MAK 475(22:2)</t>
-  </si>
-  <si>
-    <t>GIDA 415(20:3)</t>
-  </si>
-  <si>
-    <t>EEE 495(52:5)</t>
-  </si>
-  <si>
-    <t>CSE 183(14:0)</t>
-  </si>
-  <si>
-    <t>ÇEV 457(15:1)</t>
-  </si>
-  <si>
-    <t>ÇEV 207(15:1)</t>
-  </si>
-  <si>
-    <t>GIDA 243(26:3)</t>
-  </si>
-  <si>
-    <t>KPD 101(14:6)</t>
-  </si>
-  <si>
-    <t>GIDA 235(107:3)</t>
-  </si>
-  <si>
-    <t>ÇEV 461(16:1)</t>
-  </si>
-  <si>
-    <t>JEO 207(3:6)</t>
-  </si>
-  <si>
-    <t>İNM 479(21:4)</t>
-  </si>
-  <si>
-    <t>JEO 425(8:6)</t>
-  </si>
-  <si>
-    <t>JEO 301(3:6)</t>
-  </si>
-  <si>
-    <t>MAK 443(17:2)</t>
-  </si>
-  <si>
-    <t>ÇEV 403(12:1)</t>
-  </si>
-  <si>
-    <t>CSE 445(35:0)</t>
-  </si>
-  <si>
-    <t>İNM 103(65:4)</t>
-  </si>
-  <si>
-    <t>CSE 483(81:0)</t>
-  </si>
-  <si>
-    <t>CSE 321(97:0)</t>
-  </si>
-  <si>
-    <t>CSE 415(59:0)</t>
-  </si>
-  <si>
-    <t>CSE 213(110:0)</t>
-  </si>
-  <si>
-    <t>CSE 101T(154:0)</t>
-  </si>
-  <si>
-    <t>CSE 105(140:0)</t>
-  </si>
-  <si>
-    <t>MAK 429(23:2)</t>
-  </si>
-  <si>
-    <t>CSE 351(99:0)</t>
-  </si>
-  <si>
-    <t>ÇEV 303L(8:1)</t>
-  </si>
-  <si>
-    <t>JEO 103(12:6)</t>
-  </si>
-  <si>
-    <t>ÇEV 151(19:1)</t>
-  </si>
-  <si>
-    <t>CSE 203(60:0)</t>
-  </si>
-  <si>
-    <t>CSE 101L(146:0)</t>
-  </si>
-  <si>
-    <t>CSE 181(185:0)</t>
-  </si>
-  <si>
-    <t>MAK 413(21:2)</t>
-  </si>
-  <si>
-    <t>CSE 341(66:0)</t>
+    <t>MM MAK 101(190)</t>
+  </si>
+  <si>
+    <t>İM İNM 477(49)</t>
+  </si>
+  <si>
+    <t>İM İNM 211(118)</t>
+  </si>
+  <si>
+    <t>İM İNM 463(44)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 213(9)</t>
+  </si>
+  <si>
+    <t>JM JEO 407(8)</t>
+  </si>
+  <si>
+    <t>İM İNM 303(91)</t>
+  </si>
+  <si>
+    <t>MM MAK 105(121)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 183(19)</t>
+  </si>
+  <si>
+    <t>JM JEO 209(9)</t>
+  </si>
+  <si>
+    <t>MM MAK 471(20)</t>
+  </si>
+  <si>
+    <t>JM JEO 317(3)</t>
+  </si>
+  <si>
+    <t>GM GIDA 327(88)</t>
+  </si>
+  <si>
+    <t>BM CSE 435(91)</t>
+  </si>
+  <si>
+    <t>İM İNM 301(112)</t>
+  </si>
+  <si>
+    <t>EEM EEE 499(93)</t>
+  </si>
+  <si>
+    <t>İM İNM 471(10)</t>
+  </si>
+  <si>
+    <t>İM İNM 101(72)</t>
+  </si>
+  <si>
+    <t>GM GIDA 351(29)</t>
+  </si>
+  <si>
+    <t>GM GIDA 463(21)</t>
+  </si>
+  <si>
+    <t>İM İNM 491(32)</t>
+  </si>
+  <si>
+    <t>GM GIDA 101(66)</t>
+  </si>
+  <si>
+    <t>MM MAK 405(59)</t>
+  </si>
+  <si>
+    <t>JM JEO 425(8)</t>
+  </si>
+  <si>
+    <t>MM MAK 205(129)</t>
+  </si>
+  <si>
+    <t>EEM EEM 201(172)</t>
+  </si>
+  <si>
+    <t>ÇM 5i(833)</t>
+  </si>
+  <si>
+    <t>İM İNM 309(78)</t>
+  </si>
+  <si>
+    <t>BM CSE 425(28)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 179(18)</t>
+  </si>
+  <si>
+    <t>JM JEO 207(3)</t>
+  </si>
+  <si>
+    <t>İM İNM 401(65)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 315(7)</t>
+  </si>
+  <si>
+    <t>EEM EEM 305(188)</t>
+  </si>
+  <si>
+    <t>GM MAT 161(114)</t>
+  </si>
+  <si>
+    <t>GM GIDA 323(97)</t>
+  </si>
+  <si>
+    <t>EEM EEM 209(183)</t>
+  </si>
+  <si>
+    <t>BM CSE 409(56)</t>
+  </si>
+  <si>
+    <t>MM MTH 402(31)</t>
+  </si>
+  <si>
+    <t>JM JEO 307(6)</t>
+  </si>
+  <si>
+    <t>MM MAK 431(19)</t>
+  </si>
+  <si>
+    <t>BM CSE 481(91)</t>
+  </si>
+  <si>
+    <t>EEM EEE 441(64)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 353(14)</t>
+  </si>
+  <si>
+    <t>İM İNM 207(139)</t>
+  </si>
+  <si>
+    <t>MM MAK 207(109)</t>
+  </si>
+  <si>
+    <t>JM JEO 403(7)</t>
+  </si>
+  <si>
+    <t>EEM EEM 315(59)</t>
+  </si>
+  <si>
+    <t>İM İNM 473(10)</t>
+  </si>
+  <si>
+    <t>BM CSE 433(7)</t>
+  </si>
+  <si>
+    <t>JM JEO 203(2)</t>
+  </si>
+  <si>
+    <t>MM MAK 211(99)</t>
+  </si>
+  <si>
+    <t>JM JEO 405(9)</t>
+  </si>
+  <si>
+    <t>İM İNM 201(64)</t>
+  </si>
+  <si>
+    <t>MM MAK 203(123)</t>
+  </si>
+  <si>
+    <t>İM İNM 209(99)</t>
+  </si>
+  <si>
+    <t>MM MAT 161(140)</t>
+  </si>
+  <si>
+    <t>GM GIDA 457(32)</t>
+  </si>
+  <si>
+    <t>MM MAK 305(62)</t>
+  </si>
+  <si>
+    <t>MM MAK 309(70)</t>
+  </si>
+  <si>
+    <t>GM GIDA 217(111)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 307(9)</t>
+  </si>
+  <si>
+    <t>EEM EEE 447(69)</t>
+  </si>
+  <si>
+    <t>GM GIDA 357(37)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 313(9)</t>
+  </si>
+  <si>
+    <t>GM GIDA 355(37)</t>
+  </si>
+  <si>
+    <t>GM GIDA 411(32)</t>
+  </si>
+  <si>
+    <t>GM GIDA 235(107)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 303(8)</t>
+  </si>
+  <si>
+    <t>İM MAT 161(106)</t>
+  </si>
+  <si>
+    <t>İM İNM 205(152)</t>
+  </si>
+  <si>
+    <t>JM JEO 205(7)</t>
+  </si>
+  <si>
+    <t>EEM EEM 213(182)</t>
+  </si>
+  <si>
+    <t>BM CSE 381(9)</t>
+  </si>
+  <si>
+    <t>EEM EEM 215(132)</t>
+  </si>
+  <si>
+    <t>MM MAK 401(52)</t>
+  </si>
+  <si>
+    <t>MM MAK 301(124)</t>
+  </si>
+  <si>
+    <t>MM MAK 201(118)</t>
+  </si>
+  <si>
+    <t>EEM MAT 151(235)</t>
+  </si>
+  <si>
+    <t>BM FİZ 173(325)</t>
+  </si>
+  <si>
+    <t>JM JEO 201(9)</t>
+  </si>
+  <si>
+    <t>JM JEO 305(5)</t>
+  </si>
+  <si>
+    <t>GM GIDA 325(103)</t>
+  </si>
+  <si>
+    <t>GM GIDA 215(130)</t>
+  </si>
+  <si>
+    <t>MM MAK 103(102)</t>
+  </si>
+  <si>
+    <t>MM MAK 475(22)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 309(14)</t>
+  </si>
+  <si>
+    <t>JM JEO 101(16)</t>
+  </si>
+  <si>
+    <t>MM KPD 101(96)</t>
+  </si>
+  <si>
+    <t>JM KPD 101(14)</t>
+  </si>
+  <si>
+    <t>JM JEO 303(6)</t>
+  </si>
+  <si>
+    <t>EEM KPD 101(150)</t>
+  </si>
+  <si>
+    <t>EEM EEE 493(59)</t>
+  </si>
+  <si>
+    <t>JM JEO 301(3)</t>
+  </si>
+  <si>
+    <t>MM MAK 437(15)</t>
+  </si>
+  <si>
+    <t>JM JEO 321(4)</t>
+  </si>
+  <si>
+    <t>MM MAK 425(24)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 153(31)</t>
+  </si>
+  <si>
+    <t>İM İNM 311(106)</t>
+  </si>
+  <si>
+    <t>İM İNM 431(49)</t>
+  </si>
+  <si>
+    <t>BM CSE 303(83)</t>
+  </si>
+  <si>
+    <t>BM AIE 105(8)</t>
+  </si>
+  <si>
+    <t>GM GIDA 352(33)</t>
+  </si>
+  <si>
+    <t>JM JEO 409(8)</t>
+  </si>
+  <si>
+    <t>İM İNM 105(66)</t>
+  </si>
+  <si>
+    <t>MM MAK 417(20)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 173(23)</t>
+  </si>
+  <si>
+    <t>EEM EEM 391(121)</t>
+  </si>
+  <si>
+    <t>MM MAK 369(24)</t>
+  </si>
+  <si>
+    <t>GM GIDA 333(90)</t>
+  </si>
+  <si>
+    <t>MM MAK 451(20)</t>
+  </si>
+  <si>
+    <t>EEM EEE 431(10)</t>
+  </si>
+  <si>
+    <t>MM MAK 433(15)</t>
+  </si>
+  <si>
+    <t>EEM EEM 313(34)</t>
+  </si>
+  <si>
+    <t>İM İNM 307(110)</t>
+  </si>
+  <si>
+    <t>MM MAK 361(24)</t>
+  </si>
+  <si>
+    <t>EEM EEM 101(214)</t>
+  </si>
+  <si>
+    <t>MM MAK 303(105)</t>
+  </si>
+  <si>
+    <t>GM GIDA 465(35)</t>
+  </si>
+  <si>
+    <t>EEM EEM 217(137)</t>
+  </si>
+  <si>
+    <t>GM GIDA 245(45)</t>
+  </si>
+  <si>
+    <t>GM GIDA 113(76)</t>
+  </si>
+  <si>
+    <t>GM GIDA 453(29)</t>
+  </si>
+  <si>
+    <t>GM GIDA 435(72)</t>
+  </si>
+  <si>
+    <t>İM İNM 313(84)</t>
+  </si>
+  <si>
+    <t>GM GIDA 329(76)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 251(26)</t>
+  </si>
+  <si>
+    <t>GM GIDA 213(100)</t>
+  </si>
+  <si>
+    <t>GM GIDA 431(63)</t>
+  </si>
+  <si>
+    <t>GM GIDA 209(97)</t>
+  </si>
+  <si>
+    <t>İM İNM 109(65)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 253(9)</t>
+  </si>
+  <si>
+    <t>EEM EEE 487(26)</t>
+  </si>
+  <si>
+    <t>GM KİM 171(84)</t>
+  </si>
+  <si>
+    <t>EEM KİM 175(198)</t>
+  </si>
+  <si>
+    <t>BM CSE 221(132)</t>
+  </si>
+  <si>
+    <t>GM GIDA 233(81)</t>
+  </si>
+  <si>
+    <t>MM MAK 111(119)</t>
+  </si>
+  <si>
+    <t>BM CSE 301(119)</t>
+  </si>
+  <si>
+    <t>İM İNM 107(104)</t>
+  </si>
+  <si>
+    <t>BM CSE 211(93)</t>
+  </si>
+  <si>
+    <t>MM MAK 109(131)</t>
+  </si>
+  <si>
+    <t>GM GIDA 467(16)</t>
+  </si>
+  <si>
+    <t>EEM EEE 483(79)</t>
+  </si>
+  <si>
+    <t>EEM EEM 207(221)</t>
+  </si>
+  <si>
+    <t>GM GIDA 433(78)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 415(1)</t>
+  </si>
+  <si>
+    <t>GM FİZ 167(159)</t>
+  </si>
+  <si>
+    <t>BM CSE 201(99)</t>
+  </si>
+  <si>
+    <t>MM MAK 461(20)</t>
+  </si>
+  <si>
+    <t>EEM EEE 477(52)</t>
+  </si>
+  <si>
+    <t>EEM EEM 107(183)</t>
+  </si>
+  <si>
+    <t>EEM EEM 325(139)</t>
+  </si>
+  <si>
+    <t>EEM EEM 309(45)</t>
+  </si>
+  <si>
+    <t>EEM EEM 307(226)</t>
+  </si>
+  <si>
+    <t>İM İNM 203(129)</t>
+  </si>
+  <si>
+    <t>EEM EEM 357(92)</t>
+  </si>
+  <si>
+    <t>EEM EEM 341(62)</t>
+  </si>
+  <si>
+    <t>BM FİZ 175(252)</t>
+  </si>
+  <si>
+    <t>EEM EEM 323(179)</t>
+  </si>
+  <si>
+    <t>GM GIDA 451(29)</t>
+  </si>
+  <si>
+    <t>MM MAK 209(133)</t>
+  </si>
+  <si>
+    <t>BM CSE 377(27)</t>
+  </si>
+  <si>
+    <t>GM GIDA 239(115)</t>
+  </si>
+  <si>
+    <t>İM İNM 213(168)</t>
+  </si>
+  <si>
+    <t>EEM EEM 203(220)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 403(12)</t>
+  </si>
+  <si>
+    <t>İM İNM 453(47)</t>
+  </si>
+  <si>
+    <t>BM MAT 151(167)</t>
+  </si>
+  <si>
+    <t>EEM EEE 417(64)</t>
+  </si>
+  <si>
+    <t>EEM EEE 427(93)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 205(9)</t>
+  </si>
+  <si>
+    <t>EEM EEE 473(45)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 343(6)</t>
+  </si>
+  <si>
+    <t>İM İNM 433(18)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 417(8)</t>
+  </si>
+  <si>
+    <t>MM MAK 307(118)</t>
+  </si>
+  <si>
+    <t>JM JEO 309(8)</t>
+  </si>
+  <si>
+    <t>GM GIDA 199(73)</t>
+  </si>
+  <si>
+    <t>İM İNM 305(129)</t>
+  </si>
+  <si>
+    <t>BM CSE 469(11)</t>
+  </si>
+  <si>
+    <t>İM İNM 479(21)</t>
+  </si>
+  <si>
+    <t>EEM EEE 495(52)</t>
+  </si>
+  <si>
+    <t>GM GIDA 243(26)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 207(15)</t>
+  </si>
+  <si>
+    <t>GM GIDA 415(20)</t>
+  </si>
+  <si>
+    <t>BM CSE 183(14)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 409(11)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 435(17)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 457(15)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 461(16)</t>
+  </si>
+  <si>
+    <t>MM MAK 363(25)</t>
+  </si>
+  <si>
+    <t>MM MAK 443(17)</t>
+  </si>
+  <si>
+    <t>İM İNM 493(20)</t>
+  </si>
+  <si>
+    <t>MM MAK 473(19)</t>
+  </si>
+  <si>
+    <t>ÇM MAT 163(40)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 201(25)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 151(19)</t>
+  </si>
+  <si>
+    <t>BM CSE 351(99)</t>
+  </si>
+  <si>
+    <t>BM CSE 101T(154)</t>
+  </si>
+  <si>
+    <t>ÇM ÇEV 303L(8)</t>
+  </si>
+  <si>
+    <t>İM İNM 103(65)</t>
+  </si>
+  <si>
+    <t>BM CSE 445(35)</t>
+  </si>
+  <si>
+    <t>BM CSE 203(60)</t>
+  </si>
+  <si>
+    <t>BM CSE 101L(146)</t>
+  </si>
+  <si>
+    <t>JM JEO 103(12)</t>
+  </si>
+  <si>
+    <t>BM CSE 483(81)</t>
+  </si>
+  <si>
+    <t>BM CSE 105(140)</t>
+  </si>
+  <si>
+    <t>BM CSE 181(185)</t>
+  </si>
+  <si>
+    <t>BM CSE 321(97)</t>
+  </si>
+  <si>
+    <t>BM CSE 213(110)</t>
+  </si>
+  <si>
+    <t>BM CSE 415(59)</t>
+  </si>
+  <si>
+    <t>BM CSE 341(66)</t>
+  </si>
+  <si>
+    <t>MM MAK 429(23)</t>
+  </si>
+  <si>
+    <t>MM MAK 413(21)</t>
   </si>
   <si>
     <t>Day - 1</t>
@@ -794,9 +794,6 @@
   </si>
   <si>
     <t>Day - 5</t>
-  </si>
-  <si>
-    <t>Day - 6</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF55"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:32">
@@ -1263,82 +1260,79 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="L2" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="M2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="N2" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="O2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="Q2" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="R2" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="S2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="T2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V2" t="s">
+        <v>192</v>
+      </c>
+      <c r="W2" t="s">
+        <v>210</v>
+      </c>
+      <c r="X2" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z2" t="s">
         <v>228</v>
       </c>
-      <c r="V2" t="s">
-        <v>230</v>
-      </c>
-      <c r="W2" t="s">
-        <v>231</v>
-      </c>
-      <c r="X2" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>129</v>
-      </c>
       <c r="AA2" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="AB2" t="s">
         <v>237</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>254</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>254</v>
       </c>
       <c r="AF2" t="s">
         <v>255</v>
@@ -1355,82 +1349,79 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="L3" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="M3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="N3" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="O3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="Q3" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="R3" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="S3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="T3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U3" t="s">
+        <v>192</v>
+      </c>
+      <c r="V3" t="s">
+        <v>192</v>
+      </c>
+      <c r="W3" t="s">
+        <v>210</v>
+      </c>
+      <c r="X3" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z3" t="s">
         <v>228</v>
       </c>
-      <c r="V3" t="s">
-        <v>230</v>
-      </c>
-      <c r="W3" t="s">
-        <v>231</v>
-      </c>
-      <c r="X3" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>129</v>
-      </c>
       <c r="AA3" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="AB3" t="s">
         <v>237</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>254</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>254</v>
       </c>
       <c r="AF3" t="s">
         <v>255</v>
@@ -1444,76 +1435,79 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="L4" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="M4" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="N4" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="O4" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="Q4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="R4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T4" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="U4" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="V4" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="W4" t="s">
-        <v>232</v>
+        <v>211</v>
+      </c>
+      <c r="X4" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>216</v>
       </c>
       <c r="AA4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="AF4" t="s">
         <v>255</v>
@@ -1527,76 +1521,79 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="L5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="M5" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="N5" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="O5" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="P5" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="Q5" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="R5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T5" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="U5" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="V5" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="W5" t="s">
-        <v>232</v>
+        <v>211</v>
+      </c>
+      <c r="X5" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>216</v>
       </c>
       <c r="AA5" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="AF5" t="s">
         <v>255</v>
@@ -1618,70 +1615,85 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H7" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="J7" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K7" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="L7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N7" t="s">
+        <v>128</v>
+      </c>
+      <c r="O7" t="s">
         <v>158</v>
       </c>
-      <c r="M7" t="s">
-        <v>164</v>
-      </c>
-      <c r="N7" t="s">
-        <v>164</v>
-      </c>
-      <c r="O7" t="s">
-        <v>182</v>
-      </c>
       <c r="P7" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Q7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="R7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="S7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="T7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U7" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="V7" t="s">
+        <v>201</v>
+      </c>
+      <c r="W7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>229</v>
       </c>
       <c r="AA7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AB7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AC7" t="s">
-        <v>239</v>
+        <v>238</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>253</v>
       </c>
       <c r="AF7" t="s">
         <v>255</v>
@@ -1695,70 +1707,85 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="J8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" t="s">
         <v>158</v>
       </c>
-      <c r="M8" t="s">
-        <v>164</v>
-      </c>
-      <c r="N8" t="s">
-        <v>164</v>
-      </c>
-      <c r="O8" t="s">
-        <v>182</v>
-      </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Q8" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="R8" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="S8" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="T8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U8" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="V8" t="s">
+        <v>201</v>
+      </c>
+      <c r="W8" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>229</v>
       </c>
       <c r="AA8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AB8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AC8" t="s">
-        <v>239</v>
+        <v>238</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>253</v>
       </c>
       <c r="AF8" t="s">
         <v>255</v>
@@ -1772,67 +1799,82 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H9" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J9" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="K9" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M9" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" t="s">
+        <v>150</v>
+      </c>
+      <c r="O9" t="s">
         <v>159</v>
       </c>
-      <c r="M9" t="s">
+      <c r="P9" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>181</v>
+      </c>
+      <c r="R9" t="s">
+        <v>181</v>
+      </c>
+      <c r="S9" t="s">
+        <v>181</v>
+      </c>
+      <c r="T9" t="s">
+        <v>181</v>
+      </c>
+      <c r="U9" t="s">
         <v>159</v>
       </c>
-      <c r="N9" t="s">
+      <c r="V9" t="s">
         <v>159</v>
       </c>
-      <c r="O9" t="s">
-        <v>141</v>
-      </c>
-      <c r="P9" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>193</v>
-      </c>
-      <c r="R9" t="s">
-        <v>193</v>
-      </c>
-      <c r="S9" t="s">
-        <v>193</v>
-      </c>
-      <c r="T9" t="s">
-        <v>193</v>
-      </c>
-      <c r="W9" t="s">
-        <v>233</v>
+      <c r="X9" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>230</v>
       </c>
       <c r="AB9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AC9" t="s">
-        <v>240</v>
+        <v>239</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>239</v>
       </c>
       <c r="AF9" t="s">
         <v>255</v>
@@ -1846,67 +1888,82 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J10" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="K10" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M10" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" t="s">
+        <v>150</v>
+      </c>
+      <c r="O10" t="s">
         <v>159</v>
       </c>
-      <c r="M10" t="s">
+      <c r="P10" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>181</v>
+      </c>
+      <c r="R10" t="s">
+        <v>181</v>
+      </c>
+      <c r="S10" t="s">
+        <v>181</v>
+      </c>
+      <c r="T10" t="s">
+        <v>181</v>
+      </c>
+      <c r="U10" t="s">
         <v>159</v>
       </c>
-      <c r="N10" t="s">
+      <c r="V10" t="s">
         <v>159</v>
       </c>
-      <c r="O10" t="s">
-        <v>141</v>
-      </c>
-      <c r="P10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>193</v>
-      </c>
-      <c r="R10" t="s">
-        <v>193</v>
-      </c>
-      <c r="S10" t="s">
-        <v>193</v>
-      </c>
-      <c r="T10" t="s">
-        <v>193</v>
-      </c>
-      <c r="W10" t="s">
-        <v>233</v>
+      <c r="X10" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>230</v>
       </c>
       <c r="AB10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AC10" t="s">
-        <v>240</v>
+        <v>239</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>239</v>
       </c>
       <c r="AF10" t="s">
         <v>255</v>
@@ -1920,76 +1977,73 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I11" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="Q11" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="R11" t="s">
-        <v>208</v>
-      </c>
-      <c r="S11" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="T11" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="U11" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="V11" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="W11" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="X11" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="Y11" t="s">
-        <v>216</v>
+        <v>205</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>205</v>
       </c>
       <c r="AB11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF11" t="s">
         <v>256</v>
@@ -2003,76 +2057,73 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
-      </c>
-      <c r="K12" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="L12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="N12" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O12" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="Q12" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="R12" t="s">
-        <v>208</v>
-      </c>
-      <c r="S12" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="T12" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="U12" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="V12" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="W12" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="X12" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="Y12" t="s">
-        <v>216</v>
+        <v>205</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>205</v>
       </c>
       <c r="AB12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF12" t="s">
         <v>256</v>
@@ -2086,85 +2137,79 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="L13" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="M13" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="Q13" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="R13" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="S13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="T13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="U13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="V13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="W13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="X13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="Y13" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="Z13" t="s">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="AA13" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AC13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF13" t="s">
         <v>256</v>
@@ -2178,85 +2223,79 @@
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="O14" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="P14" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="Q14" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="R14" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="S14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="T14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="U14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="V14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="W14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="X14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="Y14" t="s">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="Z14" t="s">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="AA14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AC14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF14" t="s">
         <v>256</v>
@@ -2284,67 +2323,76 @@
         <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="M16" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="N16" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="O16" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Q16" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="R16" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="S16" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="T16" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="U16" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="V16" t="s">
-        <v>217</v>
+        <v>207</v>
+      </c>
+      <c r="W16" t="s">
+        <v>207</v>
+      </c>
+      <c r="X16" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>234</v>
       </c>
       <c r="AB16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AF16" t="s">
         <v>256</v>
@@ -2364,67 +2412,76 @@
         <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I17" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L17" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="N17" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Q17" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="R17" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="S17" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="T17" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="U17" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="V17" t="s">
-        <v>217</v>
+        <v>207</v>
+      </c>
+      <c r="W17" t="s">
+        <v>207</v>
+      </c>
+      <c r="X17" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>234</v>
       </c>
       <c r="AB17" t="s">
-        <v>243</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AF17" t="s">
         <v>256</v>
@@ -2447,58 +2504,70 @@
         <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J18" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="L18" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="M18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="N18" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="O18" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="Q18" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="R18" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="S18" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="T18" t="s">
+        <v>184</v>
+      </c>
+      <c r="U18" t="s">
+        <v>184</v>
+      </c>
+      <c r="V18" t="s">
+        <v>184</v>
+      </c>
+      <c r="W18" t="s">
+        <v>212</v>
+      </c>
+      <c r="X18" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y18" t="s">
         <v>225</v>
       </c>
-      <c r="AB18" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>244</v>
+      <c r="AA18" t="s">
+        <v>235</v>
       </c>
       <c r="AD18" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="AF18" t="s">
         <v>256</v>
@@ -2521,58 +2590,70 @@
         <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J19" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="L19" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="N19" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="O19" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="Q19" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="R19" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="S19" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="T19" t="s">
+        <v>184</v>
+      </c>
+      <c r="U19" t="s">
+        <v>184</v>
+      </c>
+      <c r="V19" t="s">
+        <v>184</v>
+      </c>
+      <c r="W19" t="s">
+        <v>212</v>
+      </c>
+      <c r="X19" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y19" t="s">
         <v>225</v>
       </c>
-      <c r="AB19" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>244</v>
+      <c r="AA19" t="s">
+        <v>235</v>
       </c>
       <c r="AD19" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="AF19" t="s">
         <v>256</v>
@@ -2586,52 +2667,52 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H20" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K20" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="L20" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="N20" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="O20" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="P20" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="Q20" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="R20" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="S20" t="s">
         <v>195</v>
@@ -2640,16 +2721,25 @@
         <v>195</v>
       </c>
       <c r="U20" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="V20" t="s">
         <v>195</v>
       </c>
       <c r="W20" t="s">
-        <v>195</v>
+        <v>213</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>236</v>
       </c>
       <c r="AB20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AF20" t="s">
         <v>257</v>
@@ -2663,52 +2753,52 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K21" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="M21" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="O21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="Q21" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="R21" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="S21" t="s">
         <v>195</v>
@@ -2717,16 +2807,25 @@
         <v>195</v>
       </c>
       <c r="U21" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="V21" t="s">
         <v>195</v>
       </c>
       <c r="W21" t="s">
-        <v>195</v>
+        <v>213</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>236</v>
       </c>
       <c r="AB21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AF21" t="s">
         <v>257</v>
@@ -2740,61 +2839,88 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K22" t="s">
-        <v>122</v>
+        <v>131</v>
+      </c>
+      <c r="L22" t="s">
+        <v>131</v>
       </c>
       <c r="M22" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="N22" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="O22" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="P22" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="R22" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="S22" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="T22" t="s">
-        <v>196</v>
+        <v>203</v>
+      </c>
+      <c r="U22" t="s">
+        <v>203</v>
+      </c>
+      <c r="V22" t="s">
+        <v>203</v>
+      </c>
+      <c r="W22" t="s">
+        <v>203</v>
+      </c>
+      <c r="X22" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>219</v>
       </c>
       <c r="AB22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AC22" t="s">
-        <v>246</v>
+        <v>244</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>244</v>
       </c>
       <c r="AF22" t="s">
         <v>257</v>
@@ -2808,61 +2934,88 @@
         <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K23" t="s">
-        <v>122</v>
+        <v>131</v>
+      </c>
+      <c r="L23" t="s">
+        <v>131</v>
       </c>
       <c r="M23" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="N23" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="O23" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="P23" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="Q23" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="R23" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="S23" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="T23" t="s">
-        <v>196</v>
+        <v>203</v>
+      </c>
+      <c r="U23" t="s">
+        <v>203</v>
+      </c>
+      <c r="V23" t="s">
+        <v>203</v>
+      </c>
+      <c r="W23" t="s">
+        <v>203</v>
+      </c>
+      <c r="X23" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>219</v>
       </c>
       <c r="AB23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AC23" t="s">
-        <v>246</v>
+        <v>244</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>244</v>
       </c>
       <c r="AF23" t="s">
         <v>257</v>
@@ -2884,67 +3037,88 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J25" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="K25" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="L25" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="M25" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N25" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="O25" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="Q25" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="R25" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="S25" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="T25" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="U25" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="V25" t="s">
-        <v>203</v>
+        <v>208</v>
+      </c>
+      <c r="W25" t="s">
+        <v>208</v>
+      </c>
+      <c r="X25" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>164</v>
       </c>
       <c r="AB25" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>252</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>252</v>
       </c>
       <c r="AF25" t="s">
         <v>257</v>
@@ -2958,67 +3132,88 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J26" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="L26" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="M26" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N26" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="O26" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="Q26" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="R26" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="S26" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="T26" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="U26" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="V26" t="s">
-        <v>203</v>
+        <v>208</v>
+      </c>
+      <c r="W26" t="s">
+        <v>208</v>
+      </c>
+      <c r="X26" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>164</v>
       </c>
       <c r="AB26" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>252</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>252</v>
       </c>
       <c r="AF26" t="s">
         <v>257</v>
@@ -3032,64 +3227,76 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="J27" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K27" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="M27" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="N27" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="O27" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="P27" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="Q27" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="R27" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="S27" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="T27" t="s">
-        <v>226</v>
+        <v>191</v>
+      </c>
+      <c r="U27" t="s">
+        <v>191</v>
+      </c>
+      <c r="V27" t="s">
+        <v>191</v>
+      </c>
+      <c r="W27" t="s">
+        <v>214</v>
+      </c>
+      <c r="X27" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>107</v>
       </c>
       <c r="AA27" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>248</v>
+        <v>107</v>
       </c>
       <c r="AF27" t="s">
         <v>257</v>
@@ -3103,64 +3310,76 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I28" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="J28" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K28" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="M28" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="N28" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="O28" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="P28" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="Q28" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="R28" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="S28" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="T28" t="s">
-        <v>226</v>
+        <v>191</v>
+      </c>
+      <c r="U28" t="s">
+        <v>191</v>
+      </c>
+      <c r="V28" t="s">
+        <v>191</v>
+      </c>
+      <c r="W28" t="s">
+        <v>214</v>
+      </c>
+      <c r="X28" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>107</v>
       </c>
       <c r="AA28" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>248</v>
+        <v>107</v>
       </c>
       <c r="AF28" t="s">
         <v>257</v>
@@ -3174,82 +3393,82 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K29" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="M29" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="N29" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="O29" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="P29" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Q29" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="R29" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="S29" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="T29" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="U29" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="V29" t="s">
-        <v>175</v>
-      </c>
-      <c r="W29" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="X29" t="s">
-        <v>52</v>
+        <v>221</v>
       </c>
       <c r="Y29" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="Z29" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="AA29" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="AB29" t="s">
-        <v>249</v>
+        <v>246</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>246</v>
       </c>
       <c r="AF29" t="s">
         <v>258</v>
@@ -3263,82 +3482,82 @@
         <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="J30" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K30" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="L30" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="M30" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="N30" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="O30" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Q30" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="R30" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="S30" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="T30" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="U30" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="V30" t="s">
-        <v>175</v>
-      </c>
-      <c r="W30" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="X30" t="s">
-        <v>52</v>
+        <v>221</v>
       </c>
       <c r="Y30" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="Z30" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="AA30" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="AB30" t="s">
-        <v>249</v>
+        <v>246</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>246</v>
       </c>
       <c r="AF30" t="s">
         <v>258</v>
@@ -3348,62 +3567,80 @@
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>53</v>
-      </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s">
         <v>125</v>
       </c>
-      <c r="J31" t="s">
-        <v>135</v>
-      </c>
       <c r="K31" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O31" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="P31" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="R31" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="S31" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="T31" t="s">
-        <v>219</v>
+        <v>187</v>
+      </c>
+      <c r="U31" t="s">
+        <v>187</v>
+      </c>
+      <c r="V31" t="s">
+        <v>209</v>
+      </c>
+      <c r="W31" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>138</v>
       </c>
       <c r="AB31" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>247</v>
       </c>
       <c r="AF31" t="s">
         <v>258</v>
@@ -3413,62 +3650,80 @@
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s">
         <v>125</v>
       </c>
-      <c r="J32" t="s">
-        <v>135</v>
-      </c>
       <c r="K32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="N32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O32" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="Q32" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="R32" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="S32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="T32" t="s">
-        <v>219</v>
+        <v>187</v>
+      </c>
+      <c r="U32" t="s">
+        <v>187</v>
+      </c>
+      <c r="V32" t="s">
+        <v>209</v>
+      </c>
+      <c r="W32" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>138</v>
       </c>
       <c r="AB32" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>247</v>
       </c>
       <c r="AF32" t="s">
         <v>258</v>
@@ -3487,73 +3742,82 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>64</v>
+      </c>
+      <c r="I34" t="s">
+        <v>74</v>
       </c>
       <c r="J34" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="K34" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" t="s">
         <v>147</v>
       </c>
-      <c r="M34" t="s">
-        <v>170</v>
-      </c>
       <c r="N34" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="O34" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R34" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="S34" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="T34" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="U34" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="V34" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="W34" t="s">
-        <v>54</v>
+        <v>198</v>
+      </c>
+      <c r="X34" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>198</v>
       </c>
       <c r="Z34" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>251</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>251</v>
+        <v>198</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>64</v>
       </c>
       <c r="AF34" t="s">
         <v>258</v>
@@ -3564,73 +3828,82 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="H35" t="s">
-        <v>105</v>
+        <v>64</v>
+      </c>
+      <c r="I35" t="s">
+        <v>74</v>
       </c>
       <c r="J35" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="K35" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" t="s">
+        <v>74</v>
+      </c>
+      <c r="M35" t="s">
         <v>147</v>
       </c>
-      <c r="M35" t="s">
-        <v>170</v>
-      </c>
       <c r="N35" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="O35" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R35" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="S35" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="T35" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="U35" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="V35" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="W35" t="s">
-        <v>54</v>
+        <v>198</v>
+      </c>
+      <c r="X35" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>198</v>
       </c>
       <c r="Z35" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>251</v>
+        <v>198</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>64</v>
       </c>
       <c r="AF35" t="s">
         <v>258</v>
@@ -3641,73 +3914,91 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s">
-        <v>126</v>
+        <v>118</v>
+      </c>
+      <c r="J36" t="s">
+        <v>118</v>
       </c>
       <c r="K36" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="M36" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="N36" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="O36" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q36" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="R36" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="S36" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="T36" t="s">
-        <v>227</v>
+        <v>199</v>
+      </c>
+      <c r="U36" t="s">
+        <v>199</v>
       </c>
       <c r="V36" t="s">
-        <v>93</v>
+        <v>199</v>
+      </c>
+      <c r="W36" t="s">
+        <v>215</v>
+      </c>
+      <c r="X36" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>199</v>
       </c>
       <c r="AB36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AC36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AD36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AE36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AF36" t="s">
         <v>258</v>
@@ -3718,73 +4009,91 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s">
-        <v>126</v>
+        <v>118</v>
+      </c>
+      <c r="J37" t="s">
+        <v>118</v>
       </c>
       <c r="K37" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="M37" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="N37" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="O37" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q37" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="R37" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="S37" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="T37" t="s">
-        <v>227</v>
+        <v>199</v>
+      </c>
+      <c r="U37" t="s">
+        <v>199</v>
       </c>
       <c r="V37" t="s">
-        <v>93</v>
+        <v>199</v>
+      </c>
+      <c r="W37" t="s">
+        <v>215</v>
+      </c>
+      <c r="X37" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>199</v>
       </c>
       <c r="AB37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AC37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AD37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AE37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AF37" t="s">
         <v>258</v>
@@ -3795,61 +4104,82 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="H38" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I38" t="s">
-        <v>127</v>
+        <v>65</v>
+      </c>
+      <c r="J38" t="s">
+        <v>65</v>
       </c>
       <c r="K38" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="L38" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="M38" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="N38" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="O38" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="P38" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="Q38" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="R38" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="S38" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="T38" t="s">
-        <v>115</v>
+        <v>204</v>
+      </c>
+      <c r="U38" t="s">
+        <v>204</v>
+      </c>
+      <c r="V38" t="s">
+        <v>204</v>
       </c>
       <c r="W38" t="s">
-        <v>115</v>
+        <v>204</v>
+      </c>
+      <c r="X38" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>249</v>
       </c>
       <c r="AF38" t="s">
         <v>259</v>
@@ -3860,61 +4190,82 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="G39" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="H39" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I39" t="s">
-        <v>127</v>
+        <v>65</v>
+      </c>
+      <c r="J39" t="s">
+        <v>65</v>
       </c>
       <c r="K39" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="L39" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="M39" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="N39" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="O39" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="P39" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="Q39" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="R39" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="S39" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="T39" t="s">
-        <v>115</v>
+        <v>204</v>
+      </c>
+      <c r="U39" t="s">
+        <v>204</v>
+      </c>
+      <c r="V39" t="s">
+        <v>204</v>
       </c>
       <c r="W39" t="s">
-        <v>115</v>
+        <v>204</v>
+      </c>
+      <c r="X39" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>249</v>
       </c>
       <c r="AF39" t="s">
         <v>259</v>
@@ -3924,65 +4275,80 @@
       <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B40" t="s">
-        <v>57</v>
-      </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="H40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="K40" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="M40" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="N40" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="O40" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="P40" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="Q40" t="s">
-        <v>206</v>
+        <v>66</v>
       </c>
       <c r="R40" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="S40" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="T40" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="U40" t="s">
-        <v>215</v>
+        <v>66</v>
+      </c>
+      <c r="V40" t="s">
+        <v>66</v>
+      </c>
+      <c r="W40" t="s">
+        <v>66</v>
+      </c>
+      <c r="X40" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>250</v>
       </c>
       <c r="AF40" t="s">
         <v>259</v>
@@ -3992,65 +4358,80 @@
       <c r="A41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B41" t="s">
-        <v>57</v>
-      </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
-      </c>
-      <c r="E41" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="G41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="H41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="I41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="J41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="K41" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="M41" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="N41" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="O41" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="Q41" t="s">
-        <v>206</v>
+        <v>66</v>
       </c>
       <c r="R41" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="S41" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="T41" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="U41" t="s">
-        <v>215</v>
+        <v>66</v>
+      </c>
+      <c r="V41" t="s">
+        <v>66</v>
+      </c>
+      <c r="W41" t="s">
+        <v>66</v>
+      </c>
+      <c r="X41" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>250</v>
       </c>
       <c r="AF41" t="s">
         <v>259</v>
@@ -4077,55 +4458,85 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" t="s">
         <v>85</v>
       </c>
+      <c r="F44" t="s">
+        <v>96</v>
+      </c>
       <c r="G44" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="I44" t="s">
+        <v>119</v>
       </c>
       <c r="J44" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s">
-        <v>151</v>
+        <v>96</v>
+      </c>
+      <c r="L44" t="s">
+        <v>96</v>
       </c>
       <c r="M44" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="N44" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O44" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P44" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Q44" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="R44" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="S44" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="T44" t="s">
-        <v>171</v>
+        <v>119</v>
+      </c>
+      <c r="U44" t="s">
+        <v>119</v>
+      </c>
+      <c r="V44" t="s">
+        <v>119</v>
       </c>
       <c r="W44" t="s">
-        <v>171</v>
+        <v>119</v>
+      </c>
+      <c r="X44" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>96</v>
       </c>
       <c r="Z44" t="s">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>251</v>
       </c>
       <c r="AF44" t="s">
         <v>259</v>
@@ -4136,55 +4547,85 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" t="s">
         <v>85</v>
       </c>
+      <c r="F45" t="s">
+        <v>96</v>
+      </c>
       <c r="G45" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="I45" t="s">
+        <v>119</v>
       </c>
       <c r="J45" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s">
-        <v>151</v>
+        <v>96</v>
+      </c>
+      <c r="L45" t="s">
+        <v>96</v>
       </c>
       <c r="M45" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="N45" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O45" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P45" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Q45" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="R45" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="S45" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="T45" t="s">
-        <v>171</v>
+        <v>119</v>
+      </c>
+      <c r="U45" t="s">
+        <v>119</v>
+      </c>
+      <c r="V45" t="s">
+        <v>119</v>
       </c>
       <c r="W45" t="s">
-        <v>171</v>
+        <v>119</v>
+      </c>
+      <c r="X45" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>96</v>
       </c>
       <c r="Z45" t="s">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>251</v>
       </c>
       <c r="AF45" t="s">
         <v>259</v>
@@ -4196,504 +4637,6 @@
       </c>
       <c r="AF46" t="s">
         <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32">
-      <c r="A47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" t="s">
-        <v>59</v>
-      </c>
-      <c r="E47" t="s">
-        <v>59</v>
-      </c>
-      <c r="G47" t="s">
-        <v>117</v>
-      </c>
-      <c r="H47" t="s">
-        <v>117</v>
-      </c>
-      <c r="I47" t="s">
-        <v>117</v>
-      </c>
-      <c r="J47" t="s">
-        <v>137</v>
-      </c>
-      <c r="K47" t="s">
-        <v>152</v>
-      </c>
-      <c r="L47" t="s">
-        <v>137</v>
-      </c>
-      <c r="M47" t="s">
-        <v>137</v>
-      </c>
-      <c r="N47" t="s">
-        <v>179</v>
-      </c>
-      <c r="O47" t="s">
-        <v>187</v>
-      </c>
-      <c r="P47" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>207</v>
-      </c>
-      <c r="R47" t="s">
-        <v>207</v>
-      </c>
-      <c r="S47" t="s">
-        <v>207</v>
-      </c>
-      <c r="V47" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>235</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="48" spans="1:32">
-      <c r="A48" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48" t="s">
-        <v>117</v>
-      </c>
-      <c r="H48" t="s">
-        <v>117</v>
-      </c>
-      <c r="I48" t="s">
-        <v>117</v>
-      </c>
-      <c r="J48" t="s">
-        <v>137</v>
-      </c>
-      <c r="K48" t="s">
-        <v>152</v>
-      </c>
-      <c r="L48" t="s">
-        <v>137</v>
-      </c>
-      <c r="M48" t="s">
-        <v>137</v>
-      </c>
-      <c r="N48" t="s">
-        <v>179</v>
-      </c>
-      <c r="O48" t="s">
-        <v>187</v>
-      </c>
-      <c r="P48" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>207</v>
-      </c>
-      <c r="R48" t="s">
-        <v>207</v>
-      </c>
-      <c r="S48" t="s">
-        <v>207</v>
-      </c>
-      <c r="V48" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>235</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="49" spans="1:32">
-      <c r="A49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" t="s">
-        <v>60</v>
-      </c>
-      <c r="C49" t="s">
-        <v>75</v>
-      </c>
-      <c r="G49" t="s">
-        <v>118</v>
-      </c>
-      <c r="H49" t="s">
-        <v>118</v>
-      </c>
-      <c r="J49" t="s">
-        <v>118</v>
-      </c>
-      <c r="K49" t="s">
-        <v>153</v>
-      </c>
-      <c r="L49" t="s">
-        <v>153</v>
-      </c>
-      <c r="M49" t="s">
-        <v>153</v>
-      </c>
-      <c r="N49" t="s">
-        <v>153</v>
-      </c>
-      <c r="O49" t="s">
-        <v>188</v>
-      </c>
-      <c r="P49" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>188</v>
-      </c>
-      <c r="R49" t="s">
-        <v>188</v>
-      </c>
-      <c r="S49" t="s">
-        <v>222</v>
-      </c>
-      <c r="U49" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA49" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="50" spans="1:32">
-      <c r="A50" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" t="s">
-        <v>75</v>
-      </c>
-      <c r="G50" t="s">
-        <v>118</v>
-      </c>
-      <c r="H50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J50" t="s">
-        <v>118</v>
-      </c>
-      <c r="K50" t="s">
-        <v>153</v>
-      </c>
-      <c r="L50" t="s">
-        <v>153</v>
-      </c>
-      <c r="M50" t="s">
-        <v>153</v>
-      </c>
-      <c r="N50" t="s">
-        <v>153</v>
-      </c>
-      <c r="O50" t="s">
-        <v>188</v>
-      </c>
-      <c r="P50" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>188</v>
-      </c>
-      <c r="R50" t="s">
-        <v>188</v>
-      </c>
-      <c r="S50" t="s">
-        <v>222</v>
-      </c>
-      <c r="U50" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="51" spans="1:32">
-      <c r="A51" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52" spans="1:32">
-      <c r="A52" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E52" t="s">
-        <v>95</v>
-      </c>
-      <c r="F52" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" t="s">
-        <v>95</v>
-      </c>
-      <c r="H52" t="s">
-        <v>86</v>
-      </c>
-      <c r="K52" t="s">
-        <v>154</v>
-      </c>
-      <c r="M52" t="s">
-        <v>154</v>
-      </c>
-      <c r="N52" t="s">
-        <v>154</v>
-      </c>
-      <c r="O52" t="s">
-        <v>189</v>
-      </c>
-      <c r="P52" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>189</v>
-      </c>
-      <c r="R52" t="s">
-        <v>189</v>
-      </c>
-      <c r="S52" t="s">
-        <v>223</v>
-      </c>
-      <c r="T52" t="s">
-        <v>223</v>
-      </c>
-      <c r="V52" t="s">
-        <v>86</v>
-      </c>
-      <c r="X52" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB52" t="s">
-        <v>253</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" spans="1:32">
-      <c r="A53" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" t="s">
-        <v>86</v>
-      </c>
-      <c r="E53" t="s">
-        <v>95</v>
-      </c>
-      <c r="F53" t="s">
-        <v>86</v>
-      </c>
-      <c r="G53" t="s">
-        <v>95</v>
-      </c>
-      <c r="H53" t="s">
-        <v>86</v>
-      </c>
-      <c r="K53" t="s">
-        <v>154</v>
-      </c>
-      <c r="M53" t="s">
-        <v>154</v>
-      </c>
-      <c r="N53" t="s">
-        <v>154</v>
-      </c>
-      <c r="O53" t="s">
-        <v>189</v>
-      </c>
-      <c r="P53" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>189</v>
-      </c>
-      <c r="R53" t="s">
-        <v>189</v>
-      </c>
-      <c r="S53" t="s">
-        <v>223</v>
-      </c>
-      <c r="T53" t="s">
-        <v>223</v>
-      </c>
-      <c r="V53" t="s">
-        <v>86</v>
-      </c>
-      <c r="X53" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB53" t="s">
-        <v>253</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="54" spans="1:32">
-      <c r="A54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" t="s">
-        <v>62</v>
-      </c>
-      <c r="G54" t="s">
-        <v>119</v>
-      </c>
-      <c r="H54" t="s">
-        <v>119</v>
-      </c>
-      <c r="I54" t="s">
-        <v>128</v>
-      </c>
-      <c r="J54" t="s">
-        <v>62</v>
-      </c>
-      <c r="K54" t="s">
-        <v>155</v>
-      </c>
-      <c r="N54" t="s">
-        <v>180</v>
-      </c>
-      <c r="O54" t="s">
-        <v>190</v>
-      </c>
-      <c r="P54" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>128</v>
-      </c>
-      <c r="R54" t="s">
-        <v>190</v>
-      </c>
-      <c r="T54" t="s">
-        <v>128</v>
-      </c>
-      <c r="U54" t="s">
-        <v>62</v>
-      </c>
-      <c r="V54" t="s">
-        <v>119</v>
-      </c>
-      <c r="X54" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF54" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="55" spans="1:32">
-      <c r="A55" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" t="s">
-        <v>62</v>
-      </c>
-      <c r="G55" t="s">
-        <v>119</v>
-      </c>
-      <c r="H55" t="s">
-        <v>119</v>
-      </c>
-      <c r="I55" t="s">
-        <v>128</v>
-      </c>
-      <c r="J55" t="s">
-        <v>62</v>
-      </c>
-      <c r="K55" t="s">
-        <v>155</v>
-      </c>
-      <c r="N55" t="s">
-        <v>180</v>
-      </c>
-      <c r="O55" t="s">
-        <v>190</v>
-      </c>
-      <c r="P55" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>128</v>
-      </c>
-      <c r="R55" t="s">
-        <v>190</v>
-      </c>
-      <c r="T55" t="s">
-        <v>128</v>
-      </c>
-      <c r="U55" t="s">
-        <v>62</v>
-      </c>
-      <c r="V55" t="s">
-        <v>119</v>
-      </c>
-      <c r="X55" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>
